--- a/carbon_export.xlsx
+++ b/carbon_export.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I5"/>
+  <dimension ref="A1:G4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -466,16 +466,6 @@
           <t>start_year</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
-        <is>
-          <t>reduction</t>
-        </is>
-      </c>
-      <c r="I1" s="1" t="inlineStr">
-        <is>
-          <t>increase</t>
-        </is>
-      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -498,19 +488,17 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>{'2030': 0.4}</t>
+          <t>{2030: 0.46}</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>{'checked': ['Procurement', 'Procurement &gt; Humanitarian goods', 'Procurement &gt; Humanitarian goods &gt; Blankets', 'Procurement &gt; Humanitarian goods &gt; Blankets &gt; Project 1', 'Procurement &gt; Humanitarian goods &gt; Hygienic products', 'Procurement &gt; Humanitarian goods &gt; Hygienic products &gt; Country 1', 'Service', 'Service &gt; Financial Service', 'Service &gt; Financial Service &gt; Financial service', 'Service &gt; Financial Service &gt; Financial service &gt; HQ'], 'expanded': []}</t>
+          <t>{'checked': ['Procurement', 'Procurement &gt; Humanitarian goods', 'Procurement &gt; Humanitarian goods &gt; Blankets', 'Procurement &gt; Humanitarian goods &gt; Blankets &gt; Project 1', 'Procurement &gt; Humanitarian goods &gt; Hygienic products', 'Procurement &gt; Humanitarian goods &gt; Hygienic products &gt; Country 1'], 'expanded': []}</t>
         </is>
       </c>
       <c r="G2" t="n">
         <v>2025</v>
       </c>
-      <c r="H2" t="inlineStr"/>
-      <c r="I2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -533,7 +521,7 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>{'2030': 0.2}</t>
+          <t>{2030: 0.28, 2032: 0.55}</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -544,8 +532,6 @@
       <c r="G3" t="n">
         <v>2025</v>
       </c>
-      <c r="H3" t="inlineStr"/>
-      <c r="I3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -577,51 +563,6 @@
         </is>
       </c>
       <c r="G4" t="inlineStr"/>
-      <c r="H4" t="inlineStr"/>
-      <c r="I4" t="inlineStr"/>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>Change Avion to Train</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>mixed</t>
-        </is>
-      </c>
-      <c r="C5" t="n">
-        <v>1</v>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>Value</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>{'2035': 0.3}</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>{}</t>
-        </is>
-      </c>
-      <c r="G5" t="n">
-        <v>2025</v>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>{'categories': {'checked': ['Transport &gt; Business travel &gt; To go to travel &gt; Plane', 'Transport &gt; Business travel &gt; To go to travel &gt; Plane &gt; HQ'], 'expanded': ['Transport', 'Transport &gt; Business travel', 'Transport &gt; Business travel &gt; To go to travel']}}</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>{'categories': {'checked': ['Transport &gt; Business travel &gt; To go to travel &gt; Train', 'Transport &gt; Business travel &gt; To go to travel &gt; Train &gt; HQ'], 'expanded': ['Transport', 'Transport &gt; Business travel', 'Transport &gt; Business travel &gt; To go to travel']}, 'conversion_factor': 2.0}</t>
-        </is>
-      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -634,85 +575,9 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E3"/>
+  <dimension ref="A1:A1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>name</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>mode</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>growth</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>budget</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>categories</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>testc</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>Growth %</t>
-        </is>
-      </c>
-      <c r="C2" t="n">
-        <v>2</v>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>{}</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>{'checked': ['Procurement', 'Procurement &gt; Humanitarian goods', 'Procurement &gt; Humanitarian goods &gt; Blankets', 'Procurement &gt; Humanitarian goods &gt; Blankets &gt; Project 1', 'Procurement &gt; Humanitarian goods &gt; Hygienic products', 'Procurement &gt; Humanitarian goods &gt; Hygienic products &gt; Country 1', 'Service', 'Service &gt; Financial Service', 'Service &gt; Financial Service &gt; Financial service', 'Service &gt; Financial Service &gt; Financial service &gt; HQ'], 'expanded': []}</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>tt</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>Budget Projection</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr"/>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>{'2025': 2.0, '2035': 5.0}</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>{'checked': ['Transport', 'Transport &gt; Commuting', 'Transport &gt; Commuting &gt; Bus', 'Transport &gt; Commuting &gt; Bus &gt; HQ', 'Transport &gt; Business travel', 'Transport &gt; Business travel &gt; On place travel', 'Transport &gt; Business travel &gt; On place travel &gt; Urban travel', 'Transport &gt; Business travel &gt; On place travel &gt; Urban travel &gt; Bus', 'Transport &gt; Business travel &gt; On place travel &gt; Urban travel &gt; Bus &gt; HQ', 'Transport &gt; Business travel &gt; To go to travel', 'Transport &gt; Business travel &gt; To go to travel &gt; Train', 'Transport &gt; Business travel &gt; To go to travel &gt; Train &gt; HQ', 'Transport &gt; Business travel &gt; To go to travel &gt; Plane', 'Transport &gt; Business travel &gt; To go to travel &gt; Plane &gt; HQ'], 'expanded': []}</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
+  <sheetData/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -723,7 +588,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C7"/>
+  <dimension ref="A1:C6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -750,11 +615,11 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1.13</v>
+        <v>0.99</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'checked': ['Service', 'Service &gt; Financial Service', 'Service &gt; Financial Service &gt; Financial service', 'Service &gt; Financial Service &gt; Financial service &gt; HQ'], 'expanded': []}</t>
+          <t>{'checked': [], 'expanded': []}</t>
         </is>
       </c>
     </row>
@@ -765,11 +630,11 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>2</v>
+        <v>0.97</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'checked': ['Transport', 'Transport &gt; Commuting', 'Transport &gt; Commuting &gt; Bus', 'Transport &gt; Commuting &gt; Bus &gt; HQ', 'Transport &gt; Business travel', 'Transport &gt; Business travel &gt; On place travel', 'Transport &gt; Business travel &gt; On place travel &gt; Urban travel', 'Transport &gt; Business travel &gt; On place travel &gt; Urban travel &gt; Bus', 'Transport &gt; Business travel &gt; On place travel &gt; Urban travel &gt; Bus &gt; HQ', 'Transport &gt; Business travel &gt; To go to travel', 'Transport &gt; Business travel &gt; To go to travel &gt; Train', 'Transport &gt; Business travel &gt; To go to travel &gt; Train &gt; HQ', 'Transport &gt; Business travel &gt; To go to travel &gt; Plane', 'Transport &gt; Business travel &gt; To go to travel &gt; Plane &gt; HQ'], 'expanded': []}</t>
+          <t>{'checked': [], 'expanded': []}</t>
         </is>
       </c>
     </row>
@@ -780,7 +645,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>2</v>
+        <v>0.98</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -795,7 +660,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>3.43</v>
+        <v>0.96</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -810,26 +675,11 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>2.32</v>
+        <v>0.97</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
           <t>{'checked': [], 'expanded': []}</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>test</t>
-        </is>
-      </c>
-      <c r="B7" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>{'checked': ['Procurement', 'Procurement &gt; Humanitarian goods', 'Procurement &gt; Humanitarian goods &gt; Blankets', 'Procurement &gt; Humanitarian goods &gt; Blankets &gt; Project 1', 'Procurement &gt; Humanitarian goods &gt; Hygienic products', 'Procurement &gt; Humanitarian goods &gt; Hygienic products &gt; Country 1'], 'expanded': []}</t>
         </is>
       </c>
     </row>

--- a/carbon_export.xlsx
+++ b/carbon_export.xlsx
@@ -1,39 +1,161 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <workbookPr/>
-  <workbookProtection/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
+  <workbookPr defaultThemeVersion="124226"/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Solutions" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Growth Inputs" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Structural Effects" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Solutions" sheetId="1" r:id="rId1"/>
+    <sheet name="Growth Inputs" sheetId="2" r:id="rId2"/>
+    <sheet name="Structural Effects" sheetId="3" r:id="rId3"/>
   </sheets>
-  <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="56" uniqueCount="38">
+  <si>
+    <t>id</t>
+  </si>
+  <si>
+    <t>name</t>
+  </si>
+  <si>
+    <t>type</t>
+  </si>
+  <si>
+    <t>decarbonation_potential</t>
+  </si>
+  <si>
+    <t>target</t>
+  </si>
+  <si>
+    <t>years_targets</t>
+  </si>
+  <si>
+    <t>categories</t>
+  </si>
+  <si>
+    <t>reduction</t>
+  </si>
+  <si>
+    <t>increase</t>
+  </si>
+  <si>
+    <t>description</t>
+  </si>
+  <si>
+    <t>start_year</t>
+  </si>
+  <si>
+    <t>78a25527-fcf3-4fad-b682-64ed04d3427a</t>
+  </si>
+  <si>
+    <t>01fa6984-0814-4354-bc92-5f57d87dfdc0</t>
+  </si>
+  <si>
+    <t>3d1ad7b0-a59d-4e7f-a73c-c3583c92b658</t>
+  </si>
+  <si>
+    <t>b7aa6186-f7de-4377-8f60-95531f96cec9</t>
+  </si>
+  <si>
+    <t>Business Long &gt; Premium Long</t>
+  </si>
+  <si>
+    <t>Premium Long &gt; Eco Long</t>
+  </si>
+  <si>
+    <t>Business Short &gt; Premium Short</t>
+  </si>
+  <si>
+    <t>Premium Short &gt; Eco Short</t>
+  </si>
+  <si>
+    <t>mixed</t>
+  </si>
+  <si>
+    <t>Value</t>
+  </si>
+  <si>
+    <t>{'2030': 0.5}</t>
+  </si>
+  <si>
+    <t>{}</t>
+  </si>
+  <si>
+    <t>{'categories': {'checked': ['Air Travel &gt; First &gt; Long', 'Air Travel &gt; First &gt; Long &gt; First Long', 'Air Travel &gt; First &gt; Long &gt; First Long &gt; All'], 'expanded': ['Air Travel', 'Air Travel &gt; Business', 'Air Travel &gt; First']}}</t>
+  </si>
+  <si>
+    <t>{'categories': {'checked': ['Air Travel &gt; Business &gt; Long', 'Air Travel &gt; Business &gt; Long &gt; Business Long', 'Air Travel &gt; Business &gt; Long &gt; Business Long &gt; All'], 'expanded': ['Air Travel', 'Air Travel &gt; Business', 'Air Travel &gt; First']}}</t>
+  </si>
+  <si>
+    <t>{'categories': {'checked': ['Air Travel &gt; First &gt; Short', 'Air Travel &gt; First &gt; Short &gt; First Short', 'Air Travel &gt; First &gt; Short &gt; First Short &gt; All'], 'expanded': ['Air Travel', 'Air Travel &gt; Business', 'Air Travel &gt; First']}}</t>
+  </si>
+  <si>
+    <t>{'categories': {'checked': ['Air Travel &gt; Business &gt; Short', 'Air Travel &gt; Business &gt; Short &gt; Business Short', 'Air Travel &gt; Business &gt; Short &gt; Business Short &gt; All'], 'expanded': ['Air Travel', 'Air Travel &gt; Business']}}</t>
+  </si>
+  <si>
+    <t>[{'label': 'Increase 1', 'categories': {'checked': ['Air Travel &gt; Business &gt; Long', 'Air Travel &gt; Business &gt; Long &gt; Business Long', 'Air Travel &gt; Business &gt; Long &gt; Business Long &gt; All'], 'expanded': ['Air Travel', 'Air Travel &gt; Business', 'Air Travel &gt; Economy', 'Air Travel &gt; First']}, 'conversion_factor': 1.0}]</t>
+  </si>
+  <si>
+    <t>[{'label': 'Increase 1', 'categories': {'checked': ['Air Travel &gt; Economy &gt; Long', 'Air Travel &gt; Economy &gt; Long &gt; Economy Long', 'Air Travel &gt; Economy &gt; Long &gt; Economy Long &gt; All'], 'expanded': ['Air Travel', 'Air Travel &gt; Economy']}, 'conversion_factor': 1.0}]</t>
+  </si>
+  <si>
+    <t>[{'label': 'Increase 1', 'categories': {'checked': ['Air Travel &gt; Business &gt; Short', 'Air Travel &gt; Business &gt; Short &gt; Business Short', 'Air Travel &gt; Business &gt; Short &gt; Business Short &gt; All'], 'expanded': ['Air Travel', 'Air Travel &gt; Business']}, 'conversion_factor': 1.0}]</t>
+  </si>
+  <si>
+    <t>[{'label': 'Increase 1', 'categories': {'checked': ['Air Travel &gt; Economy &gt; Short', 'Air Travel &gt; Economy &gt; Short &gt; Economy Short', 'Air Travel &gt; Economy &gt; Short &gt; Economy Short &gt; All'], 'expanded': ['Air Travel', 'Air Travel &gt; Economy']}, 'conversion_factor': 1.0}]</t>
+  </si>
+  <si>
+    <t>value</t>
+  </si>
+  <si>
+    <t>Electricity from the grid</t>
+  </si>
+  <si>
+    <t>Aviation</t>
+  </si>
+  <si>
+    <t>International maritime transport</t>
+  </si>
+  <si>
+    <t>Procurement of goods</t>
+  </si>
+  <si>
+    <t>Procurement of services</t>
+  </si>
+  <si>
+    <t>{'checked': [], 'expanded': []}</t>
+  </si>
+</sst>
+</file>
+
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
   <fonts count="2">
     <font>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
-      <color theme="1"/>
-      <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <b val="1"/>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="2">
     <fill>
-      <patternFill/>
+      <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
@@ -48,93 +170,35 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
     </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="2">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
+  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
-  <colors>
-    <indexedColors>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008000"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00808000"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="00C0C0C0"/>
-      <rgbColor rgb="00808080"/>
-      <rgbColor rgb="009999FF"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00FFFFCC"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00660066"/>
-      <rgbColor rgb="00FF8080"/>
-      <rgbColor rgb="000066CC"/>
-      <rgbColor rgb="00CCCCFF"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="0000CCFF"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00CCFFCC"/>
-      <rgbColor rgb="00FFFF99"/>
-      <rgbColor rgb="0099CCFF"/>
-      <rgbColor rgb="00FF99CC"/>
-      <rgbColor rgb="00CC99FF"/>
-      <rgbColor rgb="00FFCC99"/>
-      <rgbColor rgb="003366FF"/>
-      <rgbColor rgb="0033CCCC"/>
-      <rgbColor rgb="0099CC00"/>
-      <rgbColor rgb="00FFCC00"/>
-      <rgbColor rgb="00FF9900"/>
-      <rgbColor rgb="00FF6600"/>
-      <rgbColor rgb="00666699"/>
-      <rgbColor rgb="00969696"/>
-      <rgbColor rgb="00003366"/>
-      <rgbColor rgb="00339966"/>
-      <rgbColor rgb="00003300"/>
-      <rgbColor rgb="00333300"/>
-      <rgbColor rgb="00993300"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00333399"/>
-      <rgbColor rgb="00333333"/>
-    </indexedColors>
-  </colors>
 </styleSheet>
 </file>
 
@@ -422,268 +486,259 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:G4"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:K5"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>name</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>type</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>impact_max</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>target</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>years_targets</t>
-        </is>
-      </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>categories</t>
-        </is>
-      </c>
-      <c r="G1" s="1" t="inlineStr">
-        <is>
-          <t>start_year</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>Privilégier des fournisseurs green</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>simple</t>
-        </is>
-      </c>
-      <c r="C2" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>EF</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>{2030: 0.46}</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>{'checked': ['Procurement', 'Procurement &gt; Humanitarian goods', 'Procurement &gt; Humanitarian goods &gt; Blankets', 'Procurement &gt; Humanitarian goods &gt; Blankets &gt; Project 1', 'Procurement &gt; Humanitarian goods &gt; Hygienic products', 'Procurement &gt; Humanitarian goods &gt; Hygienic products &gt; Country 1'], 'expanded': []}</t>
-        </is>
-      </c>
-      <c r="G2" t="n">
+    <row r="1" spans="1:11">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="K1" s="1" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="2" spans="1:11">
+      <c r="A2" t="s">
+        <v>11</v>
+      </c>
+      <c r="B2" t="s">
+        <v>15</v>
+      </c>
+      <c r="C2" t="s">
+        <v>19</v>
+      </c>
+      <c r="D2">
+        <v>1</v>
+      </c>
+      <c r="E2" t="s">
+        <v>20</v>
+      </c>
+      <c r="F2" t="s">
+        <v>21</v>
+      </c>
+      <c r="G2" t="s">
+        <v>22</v>
+      </c>
+      <c r="H2" t="s">
+        <v>23</v>
+      </c>
+      <c r="I2" t="s">
+        <v>27</v>
+      </c>
+      <c r="K2">
         <v>2025</v>
       </c>
     </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>Réduction des achats</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>simple</t>
-        </is>
-      </c>
-      <c r="C3" t="n">
+    <row r="3" spans="1:11">
+      <c r="A3" t="s">
+        <v>12</v>
+      </c>
+      <c r="B3" t="s">
+        <v>16</v>
+      </c>
+      <c r="C3" t="s">
+        <v>19</v>
+      </c>
+      <c r="D3">
         <v>1</v>
       </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>Value</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>{2030: 0.28, 2032: 0.55}</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>{'checked': ['Procurement', 'Procurement &gt; Humanitarian goods', 'Procurement &gt; Humanitarian goods &gt; Blankets', 'Procurement &gt; Humanitarian goods &gt; Blankets &gt; Project 1', 'Procurement &gt; Humanitarian goods &gt; Hygienic products', 'Procurement &gt; Humanitarian goods &gt; Hygienic products &gt; Country 1'], 'expanded': []}</t>
-        </is>
-      </c>
-      <c r="G3" t="n">
+      <c r="E3" t="s">
+        <v>20</v>
+      </c>
+      <c r="F3" t="s">
+        <v>21</v>
+      </c>
+      <c r="G3" t="s">
+        <v>22</v>
+      </c>
+      <c r="H3" t="s">
+        <v>24</v>
+      </c>
+      <c r="I3" t="s">
+        <v>28</v>
+      </c>
+      <c r="K3">
         <v>2025</v>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>Prime à l'achat de vélo</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>simple</t>
-        </is>
-      </c>
-      <c r="C4" t="n">
+    <row r="4" spans="1:11">
+      <c r="A4" t="s">
+        <v>13</v>
+      </c>
+      <c r="B4" t="s">
+        <v>17</v>
+      </c>
+      <c r="C4" t="s">
+        <v>19</v>
+      </c>
+      <c r="D4">
         <v>1</v>
       </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>Value</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>{}</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>{}</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr"/>
+      <c r="E4" t="s">
+        <v>20</v>
+      </c>
+      <c r="F4" t="s">
+        <v>21</v>
+      </c>
+      <c r="G4" t="s">
+        <v>22</v>
+      </c>
+      <c r="H4" t="s">
+        <v>25</v>
+      </c>
+      <c r="I4" t="s">
+        <v>29</v>
+      </c>
+      <c r="K4">
+        <v>2025</v>
+      </c>
+    </row>
+    <row r="5" spans="1:11">
+      <c r="A5" t="s">
+        <v>14</v>
+      </c>
+      <c r="B5" t="s">
+        <v>18</v>
+      </c>
+      <c r="C5" t="s">
+        <v>19</v>
+      </c>
+      <c r="D5">
+        <v>1</v>
+      </c>
+      <c r="E5" t="s">
+        <v>20</v>
+      </c>
+      <c r="F5" t="s">
+        <v>21</v>
+      </c>
+      <c r="G5" t="s">
+        <v>22</v>
+      </c>
+      <c r="H5" t="s">
+        <v>26</v>
+      </c>
+      <c r="I5" t="s">
+        <v>30</v>
+      </c>
+      <c r="K5">
+        <v>2025</v>
+      </c>
     </row>
   </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:A1"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <sheetData/>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:C6"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>name</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>value</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>categories</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>Electricity from the grid</t>
-        </is>
-      </c>
-      <c r="B2" t="n">
-        <v>0.99</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>{'checked': [], 'expanded': []}</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>Aviation</t>
-        </is>
-      </c>
-      <c r="B3" t="n">
-        <v>0.97</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>{'checked': [], 'expanded': []}</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>International maritime transport</t>
-        </is>
-      </c>
-      <c r="B4" t="n">
-        <v>0.98</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>{'checked': [], 'expanded': []}</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>Procurement of goods</t>
-        </is>
-      </c>
-      <c r="B5" t="n">
-        <v>0.96</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>{'checked': [], 'expanded': []}</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>Procurement of services</t>
-        </is>
-      </c>
-      <c r="B6" t="n">
-        <v>0.97</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>{'checked': [], 'expanded': []}</t>
-        </is>
+    <row r="1" spans="1:3">
+      <c r="A1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3">
+      <c r="A2" t="s">
+        <v>32</v>
+      </c>
+      <c r="B2">
+        <v>-1.2</v>
+      </c>
+      <c r="C2" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3">
+      <c r="A3" t="s">
+        <v>33</v>
+      </c>
+      <c r="B3">
+        <v>-2</v>
+      </c>
+      <c r="C3" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3">
+      <c r="A4" t="s">
+        <v>34</v>
+      </c>
+      <c r="B4">
+        <v>-1</v>
+      </c>
+      <c r="C4" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3">
+      <c r="A5" t="s">
+        <v>35</v>
+      </c>
+      <c r="B5">
+        <v>-3.4</v>
+      </c>
+      <c r="C5" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3">
+      <c r="A6" t="s">
+        <v>36</v>
+      </c>
+      <c r="B6">
+        <v>-2.3</v>
+      </c>
+      <c r="C6" t="s">
+        <v>37</v>
       </c>
     </row>
   </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>